--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_22.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_22.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>NeuroType</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.628669075950103</v>
+        <v>0.2684465665501921</v>
       </c>
       <c r="C2">
-        <v>-0.1109349051537018</v>
+        <v>0.5698992374471292</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.2689578596075982</v>
+        <v>1.965469240217434</v>
       </c>
       <c r="C3">
-        <v>-0.7778522661849687</v>
+        <v>-0.0543396243019082</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.7145968563747642</v>
+        <v>-0.05236138162124385</v>
       </c>
       <c r="C4">
-        <v>0.685341922611543</v>
+        <v>0.5839815600078451</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.4308375511493679</v>
+        <v>0.01639499917891257</v>
       </c>
       <c r="C5">
-        <v>0.03114569331241107</v>
+        <v>0.02480578182990334</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.8728566597431048</v>
+        <v>-0.8057058219813455</v>
       </c>
       <c r="C6">
-        <v>-1.62895121606625</v>
+        <v>-0.3599177028192179</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-1.032185145971694</v>
+        <v>0.1885068894096603</v>
       </c>
       <c r="C7">
-        <v>0.9639140824928183</v>
+        <v>0.8091433295227927</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.635970918053733</v>
+        <v>-0.5339149760475781</v>
       </c>
       <c r="C8">
-        <v>1.840645686575767</v>
+        <v>0.07729979857463909</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.950814013306324</v>
+        <v>-0.6750380118691951</v>
       </c>
       <c r="C9">
-        <v>-1.214426189859371</v>
+        <v>0.7968675594904722</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-2.145533956375477</v>
+        <v>-1.735079279509623</v>
       </c>
       <c r="C10">
-        <v>-0.4904381197736488</v>
+        <v>0.6919227508763596</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.2746271990042056</v>
+        <v>0.3549789389215547</v>
       </c>
       <c r="C11">
-        <v>-0.803191175188311</v>
+        <v>0.07060160549721629</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.387401580255597</v>
+        <v>-2.152612808060091</v>
       </c>
       <c r="C12">
-        <v>0.3860661280746903</v>
+        <v>-1.269627908923551</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.564368247497006</v>
+        <v>-0.4621320756226082</v>
       </c>
       <c r="C13">
-        <v>-0.09151426925959319</v>
+        <v>-0.6974686052100789</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.611686240176352</v>
+        <v>-0.03066773497560416</v>
       </c>
       <c r="C14">
-        <v>2.715195685570689</v>
+        <v>0.06499775982065287</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-1.630705939553868</v>
+        <v>-0.565209404026116</v>
       </c>
       <c r="C15">
-        <v>0.9778351910294771</v>
+        <v>-0.234208673759942</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.8364445688566533</v>
+        <v>0.04975916482808816</v>
       </c>
       <c r="C16">
-        <v>0.3918992652216248</v>
+        <v>-1.658989250805032</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.03293332207341552</v>
+        <v>-0.4273275507158248</v>
       </c>
       <c r="C17">
-        <v>0.04435232679722265</v>
+        <v>-1.00640861528621</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.4111035046615137</v>
+        <v>0.61714587740916</v>
       </c>
       <c r="C18">
-        <v>-1.37627820724627</v>
+        <v>-0.5721885735150554</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.9266567520433365</v>
+        <v>-0.5831856912589766</v>
       </c>
       <c r="C19">
-        <v>-1.434400232000026</v>
+        <v>0.01530495412127184</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-1.488404999040161</v>
+        <v>1.061933386649089</v>
       </c>
       <c r="C20">
-        <v>-0.4464038870559308</v>
+        <v>1.505550615615528</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-0.422773240957479</v>
+        <v>-0.8638929329217059</v>
       </c>
       <c r="C21">
-        <v>-1.248592992566926</v>
+        <v>1.05199164243799</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-1.345099593354122</v>
+        <v>0.926938295329319</v>
       </c>
       <c r="C22">
-        <v>0.5550963793309444</v>
+        <v>0.9220301081835991</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.4130944145108725</v>
+        <v>0.9038593951566679</v>
       </c>
       <c r="C23">
-        <v>0.4159389743460885</v>
+        <v>0.1792849986451433</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.2935520331688314</v>
+        <v>0.01434284832510459</v>
       </c>
       <c r="C24">
-        <v>0.7444324472847951</v>
+        <v>-0.1305708788971154</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-1.68565590700216</v>
+        <v>-0.3279659029090577</v>
       </c>
       <c r="C25">
-        <v>0.7816470588130694</v>
+        <v>-0.04248224098828988</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.8870484172848336</v>
+        <v>-0.8237166473398485</v>
       </c>
       <c r="C26">
-        <v>1.656976354849446</v>
+        <v>0.3179255974767083</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.5214906131273805</v>
+        <v>1.185264297111019</v>
       </c>
       <c r="C27">
-        <v>-0.002571542072651756</v>
+        <v>0.9065027426820054</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.5491794312288828</v>
+        <v>-1.468020407086563</v>
       </c>
       <c r="C28">
-        <v>0.09803034781027803</v>
+        <v>-2.583862920624699</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>1.326560352729275</v>
+        <v>-1.352425128056915</v>
       </c>
       <c r="C29">
-        <v>0.6321327750804814</v>
+        <v>-0.9900773098094968</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.5254056025433493</v>
+        <v>-0.8684307073413636</v>
       </c>
       <c r="C30">
-        <v>1.787375787347871</v>
+        <v>-1.155171462618267</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.7182874267814995</v>
+        <v>-0.7476460816229723</v>
       </c>
       <c r="C31">
-        <v>-0.8195208877504514</v>
+        <v>1.098435604584252</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.8919344544434233</v>
+        <v>-0.165234077909215</v>
       </c>
       <c r="C32">
-        <v>1.322398800635562</v>
+        <v>-0.3045140421747962</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.1041059401878585</v>
+        <v>1.672652744803318</v>
       </c>
       <c r="C33">
-        <v>0.3976300225721267</v>
+        <v>0.7887484718976782</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.1710141167759986</v>
+        <v>1.533222151469392</v>
       </c>
       <c r="C34">
-        <v>0.7492087240887088</v>
+        <v>0.7605401794227419</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.6492137271878368</v>
+        <v>-0.8014208556357952</v>
       </c>
       <c r="C35">
-        <v>-1.782548359274403</v>
+        <v>-0.5349484666242255</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.2834878852218859</v>
+        <v>-0.5700273510090934</v>
       </c>
       <c r="C36">
-        <v>-0.04326444969594308</v>
+        <v>-1.33720692406409</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.389536598527991</v>
+        <v>0.8104637199426995</v>
       </c>
       <c r="C37">
-        <v>-0.03767352551726727</v>
+        <v>-0.5206766212180804</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.9160626079003151</v>
+        <v>-0.2583523305896953</v>
       </c>
       <c r="C38">
-        <v>0.8695410768958713</v>
+        <v>0.1299402340232693</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.5127650885796404</v>
+        <v>1.122029906900915</v>
       </c>
       <c r="C39">
-        <v>2.106934758763759</v>
+        <v>0.377419869180422</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-2.537217214448928</v>
+        <v>0.26910192597604</v>
       </c>
       <c r="C40">
-        <v>0.002937677722239407</v>
+        <v>-1.003180536756808</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>1.014495896409485</v>
+        <v>-0.1281117411948517</v>
       </c>
       <c r="C41">
-        <v>-1.053277457806181</v>
+        <v>-0.256238181623385</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-1.085248669242853</v>
+        <v>-0.4355596110943465</v>
       </c>
       <c r="C42">
-        <v>0.6492908123679197</v>
+        <v>0.4560579082158145</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>2.069174962698261</v>
+        <v>-0.8350866978371908</v>
       </c>
       <c r="C43">
-        <v>1.860424850544887</v>
+        <v>1.176254379754984</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-1.795590320483652</v>
+        <v>-0.6987404710088392</v>
       </c>
       <c r="C44">
-        <v>-0.3463205560355538</v>
+        <v>-0.6626112101871016</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.7590970564112374</v>
+        <v>1.049316556534426</v>
       </c>
       <c r="C45">
-        <v>0.6083493087213871</v>
+        <v>0.5921196417072878</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.127755747700805</v>
+        <v>0.6232694551752362</v>
       </c>
       <c r="C46">
-        <v>2.399128829792365</v>
+        <v>-1.23110400071354</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.6138713180222944</v>
+        <v>-0.9252691720893168</v>
       </c>
       <c r="C47">
-        <v>0.004388885113883884</v>
+        <v>0.03707612232009855</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.03263957935739278</v>
+        <v>-1.42440772053418</v>
       </c>
       <c r="C48">
-        <v>0.0546256098008872</v>
+        <v>-3.668529178645041</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.4795200874238385</v>
+        <v>0.03880126860368871</v>
       </c>
       <c r="C49">
-        <v>0.4734283021831074</v>
+        <v>0.5794390354342323</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.2790539943497851</v>
+        <v>-1.017227732042494</v>
       </c>
       <c r="C50">
-        <v>-0.1017745646417539</v>
+        <v>-0.3730999964670624</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.7024936817357391</v>
+        <v>-0.5671752276650883</v>
       </c>
       <c r="C51">
-        <v>0.6933150356884233</v>
+        <v>-2.23748140780876</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.6605712339748029</v>
+        <v>-0.4039020102980233</v>
       </c>
       <c r="C52">
-        <v>0.9421209104289885</v>
+        <v>-0.5502321776854783</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>1.83899098941469</v>
+        <v>2.151337819742239</v>
       </c>
       <c r="C53">
-        <v>0.7788113394670942</v>
+        <v>1.619604897839633</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.3545930647740431</v>
+        <v>-0.6853333162828912</v>
       </c>
       <c r="C54">
-        <v>-0.357291529530125</v>
+        <v>0.2824869087109958</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>-0.05803866686393533</v>
+        <v>-0.5263573710371082</v>
       </c>
       <c r="C55">
-        <v>3.658114465039415</v>
+        <v>-0.03485691377341249</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.2755983887573979</v>
+        <v>1.504059500301703</v>
       </c>
       <c r="C56">
-        <v>0.4899943614401892</v>
+        <v>0.3863223660659966</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>-0.7975469428877394</v>
+        <v>0.02567759187544583</v>
       </c>
       <c r="C57">
-        <v>-1.508808084921589</v>
+        <v>-1.474801832474681</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>-0.1352735647703742</v>
+        <v>1.481743876022988</v>
       </c>
       <c r="C58">
-        <v>0.8488630731188936</v>
+        <v>0.7073163221259862</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.01099236315470393</v>
+        <v>1.216875682588246</v>
       </c>
       <c r="C59">
-        <v>0.6603542386095234</v>
+        <v>0.1809020010919904</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>0.6480892452254388</v>
+        <v>1.780569965177178</v>
       </c>
       <c r="C60">
-        <v>1.213104549149917</v>
+        <v>1.571352527653331</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>-1.168080975947691</v>
+        <v>-0.586464349102592</v>
       </c>
       <c r="C61">
-        <v>-0.7082663720006586</v>
+        <v>0.3220389557930515</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.1826598896817025</v>
+        <v>-1.981985358066806</v>
       </c>
       <c r="C62">
-        <v>-0.4355056078151123</v>
+        <v>-0.2034006428365909</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.2757499464383583</v>
+        <v>-1.257749992444402</v>
       </c>
       <c r="C63">
-        <v>-0.5507080503587498</v>
+        <v>0.6172623501054265</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>-0.5415314539152493</v>
+        <v>0.6786422793900698</v>
       </c>
       <c r="C64">
-        <v>-0.4838048019884935</v>
+        <v>0.166828301647428</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>2.194569383088919</v>
+        <v>-0.9624614564413141</v>
       </c>
       <c r="C65">
-        <v>0.8153131494951551</v>
+        <v>-0.1179833896134347</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>-0.4809707856684768</v>
+        <v>0.9486328403912373</v>
       </c>
       <c r="C66">
-        <v>0.6171829937765394</v>
+        <v>0.9113835047599783</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>-1.650383424096791</v>
+        <v>-0.8559083395423414</v>
       </c>
       <c r="C67">
-        <v>-0.4887755392897108</v>
+        <v>-0.9148390415304093</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>1.64110930303657</v>
+        <v>1.199967452970661</v>
       </c>
       <c r="C68">
-        <v>0.6457241911484016</v>
+        <v>1.046220363442991</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>2.639627610483883</v>
+        <v>-0.2519689582887555</v>
       </c>
       <c r="C69">
-        <v>2.157736417132706</v>
+        <v>-1.05217089979122</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>0.4969589062599999</v>
+        <v>2.281977743246435</v>
       </c>
       <c r="C70">
-        <v>1.06948481650536</v>
+        <v>1.420147320332536</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.1734102546158955</v>
+        <v>-0.4095082443170757</v>
       </c>
       <c r="C71">
-        <v>0.7198792264785974</v>
+        <v>-0.05045425217528589</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>0.02978724638364273</v>
+        <v>0.6516038453292683</v>
       </c>
       <c r="C72">
-        <v>-0.03040844129637302</v>
+        <v>-0.938408353836425</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>-0.0490054533111102</v>
+        <v>-0.1546446311308244</v>
       </c>
       <c r="C73">
-        <v>-1.401579741089178</v>
+        <v>2.22928085225452</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>-1.025905846021785</v>
+        <v>-1.337131724202971</v>
       </c>
       <c r="C74">
-        <v>1.163072128877727</v>
+        <v>-0.9563407242828457</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>-0.03962431641470708</v>
+        <v>-1.027329853567336</v>
       </c>
       <c r="C75">
-        <v>-1.424719011094189</v>
+        <v>-1.184079964489254</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.3617991994929258</v>
+        <v>0.7107570404507324</v>
       </c>
       <c r="C76">
-        <v>0.8236613740071422</v>
+        <v>1.508957467642492</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>1.026895666699513</v>
+        <v>-0.6823536441111506</v>
       </c>
       <c r="C77">
-        <v>1.435739128829528</v>
+        <v>-1.31697122051858</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.2447007284046341</v>
+        <v>-0.6381154226276373</v>
       </c>
       <c r="C78">
-        <v>-0.1706927875504529</v>
+        <v>-0.3215570504303827</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>-0.4536610494641686</v>
+        <v>0.3128128935528859</v>
       </c>
       <c r="C79">
-        <v>-0.76177121232034</v>
+        <v>-0.5445885569882712</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>-1.224792902897365</v>
+        <v>1.821952901491582</v>
       </c>
       <c r="C80">
-        <v>0.115313718483905</v>
+        <v>1.136263254541466</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>-2.580081308734742</v>
+        <v>-2.185740842958286</v>
       </c>
       <c r="C81">
-        <v>-0.5813990633995949</v>
+        <v>-1.959924322881145</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.0588756606898545</v>
+        <v>1.133992036860348</v>
       </c>
       <c r="C82">
-        <v>-0.361145709944111</v>
+        <v>-1.059893651799471</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>0.2363574398538886</v>
+        <v>-0.3227591548361239</v>
       </c>
       <c r="C83">
-        <v>-1.136603375058095</v>
+        <v>1.21619971930996</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.5344567901850806</v>
+        <v>0.7177814544366361</v>
       </c>
       <c r="C84">
-        <v>0.2939952213157768</v>
+        <v>1.957356924479924</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>0.3139006980666227</v>
+        <v>-0.1913947898792338</v>
       </c>
       <c r="C85">
-        <v>0.4990143508622751</v>
+        <v>-0.2067565573024107</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>-0.7969917965274091</v>
+        <v>-0.7622898811728852</v>
       </c>
       <c r="C86">
-        <v>-1.04465892493885</v>
+        <v>-0.8800416627163947</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>0.6992420719554541</v>
+        <v>-1.530484305316001</v>
       </c>
       <c r="C87">
-        <v>-0.2447377708558439</v>
+        <v>-0.5708976801245726</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>-0.2484305542992483</v>
+        <v>-1.544128591127377</v>
       </c>
       <c r="C88">
-        <v>0.9499079831697821</v>
+        <v>-1.548538778693374</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>1.497627903885687</v>
+        <v>0.1495276651412411</v>
       </c>
       <c r="C89">
-        <v>-0.5290105796508296</v>
+        <v>1.042198486599516</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>-0.3233587742272628</v>
+        <v>-0.7615785623771828</v>
       </c>
       <c r="C90">
-        <v>-1.005196225113839</v>
+        <v>-0.4924587431517287</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.03041550649802141</v>
+        <v>-1.731605715466257</v>
       </c>
       <c r="C91">
-        <v>-0.8457297467223902</v>
+        <v>-0.9396745065709564</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>-1.781323832141819</v>
+        <v>0.7626050662424285</v>
       </c>
       <c r="C92">
-        <v>-2.030332597868431</v>
+        <v>0.468940774964538</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>1.196725054389392</v>
+        <v>0.2325246261679303</v>
       </c>
       <c r="C93">
-        <v>0.2785265612077287</v>
+        <v>0.521505688473035</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>-1.623752663225114</v>
+        <v>0.3414924957956034</v>
       </c>
       <c r="C94">
-        <v>-1.888910050654329</v>
+        <v>-0.2324339202237344</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>1.205417331923348</v>
+        <v>0.972216293220421</v>
       </c>
       <c r="C95">
-        <v>0.1572075611285655</v>
+        <v>2.206730034714703</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>0.03970066999340838</v>
+        <v>0.6843613944044789</v>
       </c>
       <c r="C96">
-        <v>-0.05809750875345662</v>
+        <v>0.6507132168583643</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>-1.264420312980634</v>
+        <v>0.3945466265324334</v>
       </c>
       <c r="C97">
-        <v>0.2587612646796118</v>
+        <v>1.737807221542005</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>1.754343423822459</v>
+        <v>0.8232813384667824</v>
       </c>
       <c r="C98">
-        <v>0.5171262425957666</v>
+        <v>0.004397847087211804</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>-0.3335457576003321</v>
+        <v>1.620240456499033</v>
       </c>
       <c r="C99">
-        <v>-1.503287094554562</v>
+        <v>0.5793844288342547</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>-0.05886234065215966</v>
+        <v>1.401458809966807</v>
       </c>
       <c r="C100">
-        <v>-0.8718322814040829</v>
+        <v>-0.05879236277586875</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,1310 @@
         </is>
       </c>
       <c r="B101">
-        <v>1.156706302570182</v>
+        <v>-1.284320142044863</v>
       </c>
       <c r="C101">
-        <v>0.8551224892461498</v>
+        <v>0.2374272414624224</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>-1.432749547374673</v>
+      </c>
+      <c r="C102">
+        <v>-0.1566058456165624</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>0.2041074732992143</v>
+      </c>
+      <c r="C103">
+        <v>0.1218581540745527</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>1.061978653309095</v>
+      </c>
+      <c r="C104">
+        <v>-0.6379648845123936</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>-0.04202468950436881</v>
+      </c>
+      <c r="C105">
+        <v>-0.5497585164420467</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>-1.474526959956486</v>
+      </c>
+      <c r="C106">
+        <v>0.0235987746193943</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>-0.05763265335372688</v>
+      </c>
+      <c r="C107">
+        <v>-0.01060833572234316</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>-0.06773097734357286</v>
+      </c>
+      <c r="C108">
+        <v>-0.4490379891605496</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>0.4398338409093768</v>
+      </c>
+      <c r="C109">
+        <v>1.788850650860347</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>0.7684327427010066</v>
+      </c>
+      <c r="C110">
+        <v>0.06965421148547424</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>0.8547715260277026</v>
+      </c>
+      <c r="C111">
+        <v>0.2483895136265806</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>-0.4856637277902702</v>
+      </c>
+      <c r="C112">
+        <v>-0.1130751552216973</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>0.1329838942206886</v>
+      </c>
+      <c r="C113">
+        <v>-1.260294891105201</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>0.4893806357022892</v>
+      </c>
+      <c r="C114">
+        <v>0.6298385933059687</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>0.3653232096877634</v>
+      </c>
+      <c r="C115">
+        <v>-1.317686491535048</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>-0.4971575821258319</v>
+      </c>
+      <c r="C116">
+        <v>0.2694879679289752</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>-0.2145726355163547</v>
+      </c>
+      <c r="C117">
+        <v>-0.9511305181877678</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>-0.4866293453580245</v>
+      </c>
+      <c r="C118">
+        <v>-0.07123523098899058</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>1.094728155801926</v>
+      </c>
+      <c r="C119">
+        <v>0.9684742488473754</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>0.8216153698342122</v>
+      </c>
+      <c r="C120">
+        <v>1.079229576965132</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>0.6984970479400818</v>
+      </c>
+      <c r="C121">
+        <v>-0.2069990693410653</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>-0.3397668199134202</v>
+      </c>
+      <c r="C122">
+        <v>2.073113176644611</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>0.1250291684570411</v>
+      </c>
+      <c r="C123">
+        <v>-0.3616843745196437</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>-0.03911987817011699</v>
+      </c>
+      <c r="C124">
+        <v>0.5278323834648889</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>-0.3707478611307066</v>
+      </c>
+      <c r="C125">
+        <v>0.7542800776969026</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>0.1474917994430725</v>
+      </c>
+      <c r="C126">
+        <v>-0.3781578788128687</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>0.9627986245990572</v>
+      </c>
+      <c r="C127">
+        <v>0.7637003015729302</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>-0.0870041846273281</v>
+      </c>
+      <c r="C128">
+        <v>-0.6722737709536561</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>-0.3851331911134946</v>
+      </c>
+      <c r="C129">
+        <v>-0.4325512203653693</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>-0.8811937245651061</v>
+      </c>
+      <c r="C130">
+        <v>-1.428186255142186</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>-0.6817197386767555</v>
+      </c>
+      <c r="C131">
+        <v>-1.087210939481945</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>0.3752103382059295</v>
+      </c>
+      <c r="C132">
+        <v>0.3707427378684174</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>-0.3819995405762958</v>
+      </c>
+      <c r="C133">
+        <v>-0.2364143953530286</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>1.405270926342053</v>
+      </c>
+      <c r="C134">
+        <v>0.5943219074466346</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>0.6505263854872978</v>
+      </c>
+      <c r="C135">
+        <v>0.2633951179641758</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>-0.1626741785657142</v>
+      </c>
+      <c r="C136">
+        <v>-1.449843001133059</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>-0.8396441140115022</v>
+      </c>
+      <c r="C137">
+        <v>0.946296222174269</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>-0.7210346800583545</v>
+      </c>
+      <c r="C138">
+        <v>-0.4068834439009056</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>1.234917210058041</v>
+      </c>
+      <c r="C139">
+        <v>1.89187844785779</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>1.604684392600437</v>
+      </c>
+      <c r="C140">
+        <v>0.4813562446026055</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>1.0983202703378</v>
+      </c>
+      <c r="C141">
+        <v>-0.2288576529058766</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>0.5412804102693382</v>
+      </c>
+      <c r="C142">
+        <v>0.1845169960182864</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>-1.681988565105562</v>
+      </c>
+      <c r="C143">
+        <v>-0.895963386943499</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>0.02640832732507766</v>
+      </c>
+      <c r="C144">
+        <v>-0.8272675080214521</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>1.522245858706422</v>
+      </c>
+      <c r="C145">
+        <v>0.7089196230981273</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>1.281857717439672</v>
+      </c>
+      <c r="C146">
+        <v>1.383322294969088</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>0.4436467140209607</v>
+      </c>
+      <c r="C147">
+        <v>-0.3095194020693039</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>-0.2743255648480362</v>
+      </c>
+      <c r="C148">
+        <v>-1.763916127803943</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>0.1940648202951103</v>
+      </c>
+      <c r="C149">
+        <v>-0.1285809071277179</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>1.381060512491743</v>
+      </c>
+      <c r="C150">
+        <v>0.3392735479187978</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>-0.3921708288792626</v>
+      </c>
+      <c r="C151">
+        <v>-1.306285210430488</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>1.465476707890642</v>
+      </c>
+      <c r="C152">
+        <v>-0.02027399573860778</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>-0.7318231077230448</v>
+      </c>
+      <c r="C153">
+        <v>-0.1887192516800826</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>-1.104378088391813</v>
+      </c>
+      <c r="C154">
+        <v>-1.195013978134762</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>-0.9181432240609345</v>
+      </c>
+      <c r="C155">
+        <v>-0.8789866917549551</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>0.7550319509037695</v>
+      </c>
+      <c r="C156">
+        <v>-0.6772583483613293</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>-0.953384783328928</v>
+      </c>
+      <c r="C157">
+        <v>0.8440567888482077</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>1.566771827081546</v>
+      </c>
+      <c r="C158">
+        <v>0.03293600068600444</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>-0.6942914700644289</v>
+      </c>
+      <c r="C159">
+        <v>-0.5756681235225887</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>-0.09617204528556073</v>
+      </c>
+      <c r="C160">
+        <v>-0.3330412920932418</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>0.2128492535057675</v>
+      </c>
+      <c r="C161">
+        <v>0.4754990391471074</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>1.349548945011581</v>
+      </c>
+      <c r="C162">
+        <v>1.067021673062718</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>-0.2590466884419039</v>
+      </c>
+      <c r="C163">
+        <v>0.09809938004370267</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>-1.622667747721716</v>
+      </c>
+      <c r="C164">
+        <v>-0.6116503954303663</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>1.135844074226959</v>
+      </c>
+      <c r="C165">
+        <v>-0.1552890660598795</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>-0.8707527227133854</v>
+      </c>
+      <c r="C166">
+        <v>-0.6902686124858082</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>-0.5585916862652528</v>
+      </c>
+      <c r="C167">
+        <v>0.7236823560710123</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>0.1009655424739158</v>
+      </c>
+      <c r="C168">
+        <v>-1.627737249397828</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>-0.7779595635622747</v>
+      </c>
+      <c r="C169">
+        <v>1.428893383822346</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>-1.180629731585436</v>
+      </c>
+      <c r="C170">
+        <v>-0.01793027602030273</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>0.6041496975096207</v>
+      </c>
+      <c r="C171">
+        <v>-0.9451380322182472</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>-0.2539155314114949</v>
+      </c>
+      <c r="C172">
+        <v>-1.789974648109911</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>0.9200906070679478</v>
+      </c>
+      <c r="C173">
+        <v>0.1514782256902969</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>-0.5945696884178687</v>
+      </c>
+      <c r="C174">
+        <v>-0.007844624954884222</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>-0.5283216511695101</v>
+      </c>
+      <c r="C175">
+        <v>0.219400097981637</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>-0.5398029379288098</v>
+      </c>
+      <c r="C176">
+        <v>0.3798476558574476</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>-1.450914168275575</v>
+      </c>
+      <c r="C177">
+        <v>-0.5542824357116192</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>0.1266559859809616</v>
+      </c>
+      <c r="C178">
+        <v>-1.240847568390276</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>1.800756983029365</v>
+      </c>
+      <c r="C179">
+        <v>-0.3404922513699934</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>1.725323278489591</v>
+      </c>
+      <c r="C180">
+        <v>-0.8693985079827822</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>-0.6906302718963061</v>
+      </c>
+      <c r="C181">
+        <v>0.3821435452835573</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>0.7044241111711822</v>
+      </c>
+      <c r="C182">
+        <v>-1.403734850237041</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>-1.123670603041349</v>
+      </c>
+      <c r="C183">
+        <v>0.2354231654402201</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>0.701684924571334</v>
+      </c>
+      <c r="C184">
+        <v>0.7817251761447068</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>-1.563592882467691</v>
+      </c>
+      <c r="C185">
+        <v>-0.4189691479620596</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>0.9769723365201936</v>
+      </c>
+      <c r="C186">
+        <v>1.456588406771391</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>-0.6226875736065709</v>
+      </c>
+      <c r="C187">
+        <v>0.793304890634099</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>-1.018146688405984</v>
+      </c>
+      <c r="C188">
+        <v>-1.099296253828419</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>-0.7247699460875408</v>
+      </c>
+      <c r="C189">
+        <v>0.5398194240797727</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>-0.5012801039177512</v>
+      </c>
+      <c r="C190">
+        <v>-1.733634620485166</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>0.9008385045132008</v>
+      </c>
+      <c r="C191">
+        <v>-1.254628849254503</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>0.3352756836350921</v>
+      </c>
+      <c r="C192">
+        <v>0.06003485508821221</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>0.4941403147553002</v>
+      </c>
+      <c r="C193">
+        <v>-0.3329999948963501</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>0.2525050951237233</v>
+      </c>
+      <c r="C194">
+        <v>-0.072194474748008</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>-0.749770120045179</v>
+      </c>
+      <c r="C195">
+        <v>0.912580441776784</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>2.884111557511019</v>
+      </c>
+      <c r="C196">
+        <v>1.779195131869754</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>0.4502520792378473</v>
+      </c>
+      <c r="C197">
+        <v>0.1458258517564948</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>0.05485028437812987</v>
+      </c>
+      <c r="C198">
+        <v>-1.300302754252185</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>0.9979460200587347</v>
+      </c>
+      <c r="C199">
+        <v>1.067834268305217</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>0.4038849250434028</v>
+      </c>
+      <c r="C200">
+        <v>-1.197170276635008</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>-0.6951579360799982</v>
+      </c>
+      <c r="C201">
+        <v>-0.3362641240154504</v>
       </c>
     </row>
   </sheetData>
